--- a/00_Executive_Rollup_Report/AMEX_RiskIQ_Platform_Executive_Rollup_Workbook.xlsx
+++ b/00_Executive_Rollup_Report/AMEX_RiskIQ_Platform_Executive_Rollup_Workbook.xlsx
@@ -23,9 +23,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="164" formatCode="[&gt;=1000000000]$0.00,,,&quot;B&quot;;[&gt;=1000000]$0.00,,&quot;M&quot;;&quot;$&quot;#,##0;(&quot;$&quot;#,##0)"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,6 +65,18 @@
       <b val="1"/>
       <color rgb="000B1F3A"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00C41E3A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="000B1F3A"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -128,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -145,8 +157,14 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -701,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F12"/>
+  <dimension ref="B2:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -731,10 +749,8 @@
           <t>Total Platform Net Value / Cycle</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>$432,132,849</t>
-        </is>
+      <c r="D5" s="4" t="n">
+        <v>432132848.85</v>
       </c>
     </row>
     <row r="6">
@@ -743,10 +759,8 @@
           <t>Reserve-Optimization Value (Separate)</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>$4,617,593</t>
-        </is>
+      <c r="D6" s="5" t="n">
+        <v>4617593.08</v>
       </c>
     </row>
     <row r="7">
@@ -796,6 +810,16 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>1-Year Projected Net Value (ASSUMPTION, 12x/yr)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>5185594186.2</v>
+      </c>
+    </row>
     <row r="12">
       <c r="B12" s="8" t="inlineStr">
         <is>
@@ -803,17 +827,36 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>UNAUDITED RESULTS -- every figure on this report is a real, computed internal management estimate from this platform's own notebooks, not a certified or externally audited financial statement. Figures are shown in $M/$B shorthand for readability; the exact underlying value is always available in this platform's own persisted JSON artifacts for audit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>ASSUMPTION: projects the current real $$432.13M/cycle run-rate at a 12-cycle/year (monthly) cadence, flat, for 1/3/5 years -- an extrapolation of today's real measured figure, not a certified multi-year forecast.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="14">
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="B2:F2"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D13:E13"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="D12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -834,17 +877,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Source / Rationale</t>
         </is>
@@ -856,10 +899,10 @@
           <t>Review Minutes Per Report Separately</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n">
+      <c r="B2" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>ASSUMPTION -- estimated minutes a CRO/head-of-risk (or their team) spends reviewing ONE problem's own report/dashboard/service output before this platform existed. Edit to your institution's real observed review time.</t>
         </is>
@@ -871,10 +914,10 @@
           <t>Review Minutes Unified Dashboard</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>ASSUMPTION -- estimated minutes to review the single unified executive dashboard covering all 13 problems (this notebook's own deliverable), replacing 13 separate reviews.</t>
         </is>
@@ -886,10 +929,10 @@
           <t>Executive Hourly Cost Usd</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="14" t="n">
         <v>350</v>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>ASSUMPTION -- blended fully-loaded hourly cost of the executive(s)/senior-analyst reviewers involved (CRO-tier). Edit to your institution's real comp figures.</t>
         </is>
@@ -901,10 +944,10 @@
           <t>Reviewers Per Cycle</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>ASSUMPTION -- number of senior stakeholders (e.g. CRO + 2 direct reports) who each separately reviewed the prior 13-report format and now review the unified dashboard instead.</t>
         </is>
@@ -916,10 +959,10 @@
           <t>Dashboard Hosting Cost Usd Per Cycle</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>ASSUMPTION -- ongoing hosting/maintenance cost for the unified executive dashboard service per cycle, the genuinely new recurring cost this problem introduces (same treatment as Problem 12's ongoing-hosting-cost stream).</t>
         </is>
@@ -931,10 +974,10 @@
           <t>Implementation Cost Usd</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="14" t="n">
         <v>30000</v>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>ASSUMPTION -- one-time build/integration cost for the unified executive dashboard (BI aggregation layer, deployed API, reporting pipeline).</t>
         </is>
@@ -946,10 +989,10 @@
           <t>Annual Application Cycles</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>ASSUMPTION -- monthly executive review cadence, matching this platform's other ongoing-monitoring problems' cadence.</t>
         </is>
@@ -981,32 +1024,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Problem #</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Phase</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Financial Value / Cycle (USD)</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1031,8 +1074,8 @@
           <t>foundational_model</t>
         </is>
       </c>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="14" t="inlineStr">
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>FOUNDATIONAL / N/A</t>
         </is>
@@ -1057,8 +1100,8 @@
           <t>foundational_model</t>
         </is>
       </c>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="14" t="inlineStr">
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>FOUNDATIONAL / N/A</t>
         </is>
@@ -1083,10 +1126,10 @@
           <t>reserve_optimization</t>
         </is>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="15" t="n">
         <v>4617593.08</v>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1111,10 +1154,10 @@
           <t>value_creation</t>
         </is>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="15" t="n">
         <v>9690840</v>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1139,10 +1182,10 @@
           <t>value_creation</t>
         </is>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="15" t="n">
         <v>4898250</v>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1167,10 +1210,10 @@
           <t>value_creation</t>
         </is>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="15" t="n">
         <v>8491170</v>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1195,10 +1238,10 @@
           <t>value_creation</t>
         </is>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="15" t="n">
         <v>2912145</v>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1223,10 +1266,10 @@
           <t>value_creation</t>
         </is>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="15" t="n">
         <v>315820</v>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1251,10 +1294,10 @@
           <t>value_creation</t>
         </is>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="15" t="n">
         <v>341908210</v>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1279,10 +1322,10 @@
           <t>value_creation</t>
         </is>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="15" t="n">
         <v>2206596.12</v>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1307,10 +1350,10 @@
           <t>value_creation</t>
         </is>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="15" t="n">
         <v>2374108.15</v>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1335,10 +1378,10 @@
           <t>value_creation</t>
         </is>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="15" t="n">
         <v>1275022</v>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1363,10 +1406,10 @@
           <t>value_creation</t>
         </is>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="15" t="n">
         <v>58060687.58</v>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1406,22 +1449,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Risk Grade \ Profitability Tier</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Low Profitability</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Medium Profitability</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>High Profitability</t>
         </is>
@@ -1433,13 +1476,13 @@
           <t>Low Risk</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="18" t="n">
         <v>3070</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="18" t="n">
         <v>145942</v>
       </c>
     </row>
@@ -1449,13 +1492,13 @@
           <t>Medium Risk</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="18" t="n">
         <v>546</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="18" t="n">
         <v>145649</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="18" t="n">
         <v>3091</v>
       </c>
     </row>
@@ -1465,13 +1508,13 @@
           <t>High Risk</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="18" t="n">
         <v>148855</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="18" t="n">
         <v>542</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1527,17 +1570,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Problem #</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1552,7 +1595,7 @@
           <t>Credit Scoring (Static PD)</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>FOUNDATIONAL / N/A</t>
         </is>
@@ -1567,7 +1610,7 @@
           <t>Risk Tier Classification</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>FOUNDATIONAL / N/A</t>
         </is>
@@ -1582,7 +1625,7 @@
           <t>Expected Credit Loss (IFRS9/CECL)</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1597,7 +1640,7 @@
           <t>Delinquency Escalation / Loss Severity</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1612,7 +1655,7 @@
           <t>Early Payment Default Detection</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1627,7 +1670,7 @@
           <t>Dynamic / Behavioral Credit Scoring</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1642,7 +1685,7 @@
           <t>Early Warning System</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1657,7 +1700,7 @@
           <t>Roll-Rate Modeling</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1672,7 +1715,7 @@
           <t>Collections Optimization</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1687,7 +1730,7 @@
           <t>Credit Line Management</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1702,7 +1745,7 @@
           <t>Real-Time Portfolio Monitoring</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1717,7 +1760,7 @@
           <t>360 Degree Customer Intelligence</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1732,7 +1775,7 @@
           <t>Risk-Adjusted Profitability Modeling</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>RECOMMENDED</t>
         </is>
@@ -1760,12 +1803,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -1809,7 +1852,7 @@
           <t>Gross Time-Savings / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="15">
         <f>(B4/60)*Assumptions!$B$4*Assumptions!$B$5</f>
         <v/>
       </c>
@@ -1820,7 +1863,7 @@
           <t>Net Benefit / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="15">
         <f>B5-Assumptions!$B$6</f>
         <v/>
       </c>
@@ -1831,7 +1874,7 @@
           <t>Annual Net Benefit (USD)</t>
         </is>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="15">
         <f>B6*Assumptions!$B$8</f>
         <v/>
       </c>
@@ -1859,12 +1902,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Org Level</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Suggestion</t>
         </is>
@@ -1876,7 +1919,7 @@
           <t>Data/ML Engineer</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Schedule Notebooks 70-72 to re-run automatically after every one of the 13 upstream problems' own scheduled re-run, so the executive dashboard's $432,132,849/cycle headline is never more than one upstream refresh stale.</t>
         </is>
@@ -1888,7 +1931,7 @@
           <t>Risk Analyst</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Use the Problem Registry tab's phase/category filters to spot-check any single problem's real financial_value_usd against that problem's own Financial Impact report before citing the platform total in a memo.</t>
         </is>
@@ -1900,7 +1943,7 @@
           <t>Collections/Ops Manager</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>Cross-reference the Risk-Profitability Map tab against your team's current worklists -- the real High-Risk/Low-Profitability cell is exactly Problem 13's own targeted cross-tier segment.</t>
         </is>
@@ -1912,7 +1955,7 @@
           <t>Head of Model Risk Management</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Treat the 3 excluded problems ([1, 2, 3]) as your MRM committee's standing agenda item: Problems [1, 2] are foundational risk models whose value is realized entirely downstream; and Problem [3] is reserve-optimization gain kept as its own distinct $4,617,593 line. None is currently a held-out-pending-KPI-review case -- re-check this each cycle, since that can change as problems are re-verified.</t>
         </is>
@@ -1924,7 +1967,7 @@
           <t>CRO / Head of Risk</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>This dashboard is the single artifact for board-level reporting: $432,132,849/cycle in real, non-double-counted platform value across 10 production-recommended systems, plus real portfolio exposure context from Problem 1's Basel/IFRS9 mapping -- reviewed in one sitting instead of 13 separate ones.</t>
         </is>
@@ -1936,7 +1979,7 @@
           <t>Board / Audit Committee</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Request the Policy &amp; Validation tab's aggregation_completeness and aggregation_scope_correctness KPI results each quarter -- these two checks are what prove this dashboard's headline number is not double-counted or miscategorized, the exact failure mode board-level financial rollups are most exposed to.</t>
         </is>
